--- a/tools/importer/reports/import-americanhome-subpage.report.xlsx
+++ b/tools/importer/reports/import-americanhome-subpage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,6 +61,21 @@
     <t>https://www.americanhome.co.jp/home/customers/claim</t>
   </si>
   <si>
+    <t>home/customers/confirmation.report.json</t>
+  </si>
+  <si>
+    <t>home/customers/confirmation</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:07:44.474Z</t>
+  </si>
+  <si>
+    <t>ご契約内容の確認・変更｜アメリカンホーム保険会社</t>
+  </si>
+  <si>
+    <t>https://www.americanhome.co.jp/home/customers/confirmation</t>
+  </si>
+  <si>
     <t>home/customers/deduction.report.json</t>
   </si>
   <si>
@@ -74,6 +89,39 @@
   </si>
   <si>
     <t>https://www.americanhome.co.jp/home/customers/deduction</t>
+  </si>
+  <si>
+    <t>home/customers/disability.report.json</t>
+  </si>
+  <si>
+    <t>["columns-gray-box"]</t>
+  </si>
+  <si>
+    <t>home/customers/disability</t>
+  </si>
+  <si>
+    <t>2026-03-10T11:57:52.315Z</t>
+  </si>
+  <si>
+    <t>耳や言葉、目の不自由なお客さま｜アメリカンホーム保険会社</t>
+  </si>
+  <si>
+    <t>https://www.americanhome.co.jp/home/customers/disability</t>
+  </si>
+  <si>
+    <t>home/customers/family-registration.report.json</t>
+  </si>
+  <si>
+    <t>home/customers/family-registration</t>
+  </si>
+  <si>
+    <t>2026-03-10T16:22:41.972Z</t>
+  </si>
+  <si>
+    <t>ご家族情報登録制度｜アメリカンホーム保険会社</t>
+  </si>
+  <si>
+    <t>https://www.americanhome.co.jp/home/customers/family_registration</t>
   </si>
 </sst>
 </file>
@@ -462,15 +510,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -550,6 +598,84 @@
       </c>
       <c r="H3" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
